--- a/Trabalho/procurados.xlsx
+++ b/Trabalho/procurados.xlsx
@@ -28,7 +28,7 @@
     <t>Roubo de copias de Mineirinho Ultra Adventures</t>
   </si>
   <si>
-    <t>Cauã Olivar</t>
+    <t>Caua Olivar</t>
   </si>
   <si>
     <t>Atentado ao pudor</t>
